--- a/backend/data/financials_by_company/0039.HK.xlsx
+++ b/backend/data/financials_by_company/0039.HK.xlsx
@@ -3690,187 +3690,187 @@
       </c>
       <c r="DA1" t="inlineStr">
         <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>marketState</t>
         </is>
       </c>
       <c r="EL1" t="inlineStr">
@@ -4003,7 +4003,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.121</v>
+        <v>-0.136</v>
       </c>
       <c r="AF2" t="n">
         <v>34368000</v>
@@ -4012,7 +4012,7 @@
         <v>34368000</v>
       </c>
       <c r="AH2" t="n">
-        <v>2804677</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -4057,7 +4057,7 @@
         <v>0.045</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.072605</v>
+        <v>0.070885</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
@@ -4130,10 +4130,10 @@
         <v>-17.873</v>
       </c>
       <c r="BT2" t="n">
-        <v>-0.6017699</v>
+        <v>-0.5408163</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="BV2" t="n">
         <v>0.01375</v>
@@ -4246,140 +4246,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="DA2" t="n">
+        <v>-0.0009999983000000001</v>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
+          <t>0.043 - 0.051</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DC2" t="n">
-        <v>2804677</v>
-      </c>
       <c r="DD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE2" t="n">
         <v>0.0020000003</v>
       </c>
-      <c r="DE2" t="n">
+      <c r="DF2" t="n">
         <v>0.046511635</v>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>0.043 - 0.166</t>
         </is>
       </c>
-      <c r="DG2" t="n">
+      <c r="DH2" t="n">
         <v>-0.12099999</v>
       </c>
-      <c r="DH2" t="n">
+      <c r="DI2" t="n">
         <v>-0.72891563</v>
       </c>
-      <c r="DI2" t="n">
-        <v>-60.176994</v>
-      </c>
       <c r="DJ2" t="n">
-        <v>1743432759</v>
+        <v>-54.08163</v>
       </c>
       <c r="DK2" t="n">
         <v>1743432759</v>
       </c>
-      <c r="DL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="n">
+      <c r="DL2" t="n">
+        <v>1743432759</v>
+      </c>
+      <c r="DM2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DN2" t="n">
         <v>-0.01</v>
       </c>
-      <c r="DN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="n">
+      <c r="DO2" t="b">
         <v>0</v>
       </c>
       <c r="DP2" t="n">
-        <v>-0.027604997</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-0.38020796</v>
-      </c>
-      <c r="DR2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DS2" t="n">
         <v>979695000000</v>
       </c>
-      <c r="DT2" t="n">
-        <v>-0.0009999983000000001</v>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>0.043 - 0.051</t>
-        </is>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DR2" t="n">
+        <v>1774943997</v>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>CH BEIDAHUANG</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>China Beidahuang Industry Group Holdings Limited</t>
+        </is>
+      </c>
+      <c r="DU2" t="n">
+        <v>-2.1739094</v>
       </c>
       <c r="DV2" t="n">
-        <v>1774943997</v>
+        <v>0.045</v>
       </c>
       <c r="DW2" t="inlineStr">
         <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DX2" t="inlineStr">
+      <c r="DY2" t="inlineStr">
         <is>
           <t>finmb_9736054</t>
         </is>
       </c>
-      <c r="DY2" t="inlineStr">
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DZ2" t="inlineStr">
+      <c r="EA2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="EA2" t="n">
+      <c r="EB2" t="n">
         <v>28800000</v>
       </c>
-      <c r="EB2" t="inlineStr">
+      <c r="EC2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="EC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>China Beidahuang Industry Group Holdings Limited</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>CH BEIDAHUANG</t>
-        </is>
+      <c r="ED2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>0</v>
       </c>
       <c r="EF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.025885</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>-0.36516893</v>
+      </c>
+      <c r="EI2" t="n">
         <v>15</v>
       </c>
-      <c r="EG2" t="n">
+      <c r="EJ2" t="n">
         <v>15</v>
       </c>
-      <c r="EH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>-2.1739094</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
+      <c r="EK2" t="b">
+        <v>0</v>
       </c>
       <c r="EL2" t="inlineStr"/>
     </row>
